--- a/Wykresy_z2.xlsx
+++ b/Wykresy_z2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\studia_aisd\algorytmy_sortowania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5029A0A0-9E80-479B-8CE0-B379EA0689D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBF2838-8F51-4AFB-85DB-B7A435DF3F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
   </bookViews>
   <sheets>
     <sheet name="create" sheetId="1" r:id="rId1"/>
@@ -84,11 +84,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -184,7 +186,7 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -210,7 +212,19 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -219,49 +233,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>6000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>12000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>14000</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>30000</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -272,10 +286,55 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8969999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.0650000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11246</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16563</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.24306</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.32597999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.42725999999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.54071000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.67457</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.81305000000000005</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.99312</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1511499999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.36422</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5779000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-0969-4D5F-A629-F0CBE8D274C5}"/>
@@ -306,7 +365,19 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -315,49 +386,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>6000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>12000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>14000</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>30000</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -366,294 +437,60 @@
             <c:numRef>
               <c:f>create!$C$2:$C$16</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>3.0500000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.3100000000000006E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9599999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.3090000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.7370000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.2679999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.10063</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.13117000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.17502000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.21023</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.27510000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.32073000000000002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.38468999999999998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.45236999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.51902999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-0969-4D5F-A629-F0CBE8D274C5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>create!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>create!$A$2:$A$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>12000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>14000</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>30000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>create!$D$2:$D$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0969-4D5F-A629-F0CBE8D274C5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>create!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>create!$A$2:$A$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>12000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>14000</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>30000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>create!$E$2:$E$16</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-0969-4D5F-A629-F0CBE8D274C5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>create!$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="7030A0"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>create!$A$2:$A$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>12000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>14000</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>30000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>create!$F$2:$F$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-0969-4D5F-A629-F0CBE8D274C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -673,8 +510,8 @@
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
-          <c:max val="20000"/>
-          <c:min val="5000"/>
+          <c:max val="16000"/>
+          <c:min val="1000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -754,7 +591,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -944,7 +781,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pl-PL"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -952,7 +789,7 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -978,7 +815,19 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -987,49 +836,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>6000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>12000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>14000</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>30000</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1040,10 +889,55 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.098E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.5809999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10169</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17945</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.27944999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.38246999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52719000000000005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.70315000000000005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.88338000000000005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.09884</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.36015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6630100000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.97478</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.34335</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.73854</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-DDE3-49A8-A840-7A9A7B9D6E93}"/>
@@ -1074,7 +968,19 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -1083,49 +989,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>6000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>12000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>14000</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>30000</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1136,10 +1042,55 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.0499999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2599999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.6899999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.332E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9290000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.2799999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.1180000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.4949999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.3660000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.7879999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.11326</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.14346999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.17679</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.20202000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.24174999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-DDE3-49A8-A840-7A9A7B9D6E93}"/>
@@ -1162,8 +1113,8 @@
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
-          <c:max val="20000"/>
-          <c:min val="5000"/>
+          <c:max val="16000"/>
+          <c:min val="1000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1433,15 +1384,25 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pl-PL"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.4109630562333648E-2"/>
+          <c:y val="0.11001852626937178"/>
+          <c:w val="0.88728190013606989"/>
+          <c:h val="0.75331590325606423"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1467,7 +1428,19 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -1476,49 +1449,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>6000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>12000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>14000</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>30000</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1529,10 +1502,55 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>8.3199999608041199E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.27400000565103E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8180000006395799E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5159999950119501E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9709999944316202E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.53399999767134E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.1819999933068097E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.7510000058537099E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.6229999972856604E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.70499999614548E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.6390000049286703E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.2920000022568205E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.6589999955322093E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.9970000044559094E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.69400000030873E-3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-6C18-4AB7-874A-8623EB59C5AB}"/>
@@ -1563,7 +1581,19 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -1572,49 +1602,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>6000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>12000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>14000</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>30000</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1625,10 +1655,55 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.6577999997243699E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.4587999990617304E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.84257000000798E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.13871999987895E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.7633199999836499E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.3047699999733595E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.100573699999586</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.13349120000020701</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.17780250000032499</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.227332300000853</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.26611559999946599</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.33415179999974498</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.38591469999846501</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.45124240000040999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.54056039999886696</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-6C18-4AB7-874A-8623EB59C5AB}"/>
@@ -1651,8 +1726,8 @@
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
-          <c:max val="160000"/>
-          <c:min val="10000"/>
+          <c:max val="16000"/>
+          <c:min val="1000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1922,7 +1997,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pl-PL"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1930,7 +2005,7 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1949,14 +2024,26 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="00B0F0"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -1965,49 +2052,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>6000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>12000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>14000</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>30000</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2016,12 +2103,57 @@
             <c:numRef>
               <c:f>height!$B$2:$B$16</c:f>
               <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>204</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-8F23-43BC-9E7A-09DB3455A3DB}"/>
@@ -2045,14 +2177,26 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -2061,49 +2205,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2000</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4000</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>6000</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>8000</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>10000</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>12000</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>14000</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>28000</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>30000</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2112,12 +2256,57 @@
             <c:numRef>
               <c:f>height!$C$2:$C$16</c:f>
               <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-8F23-43BC-9E7A-09DB3455A3DB}"/>
@@ -2140,8 +2329,8 @@
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
-          <c:max val="160000"/>
-          <c:min val="10000"/>
+          <c:max val="16000"/>
+          <c:min val="1000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2221,7 +2410,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4573,16 +4762,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>4761</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>705678</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>21327</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>86553</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>83240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4614,16 +4803,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>732597</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>177662</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>298174</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>182424</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4655,16 +4844,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>754959</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>113679</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>13667</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4696,15 +4885,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>482047</xdr:colOff>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>69573</xdr:colOff>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5030,7 +5219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30C56E8-06B5-4DC8-9A83-1482F52FEB5E}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -5039,7 +5228,7 @@
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -5047,9 +5236,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2000</v>
+        <v>1000</v>
+      </c>
+      <c r="B2" s="2">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>3.0500000000000002E-3</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -5058,11 +5253,17 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4000</v>
-      </c>
-      <c r="B3" s="2"/>
+        <f>A2+1000</f>
+        <v>2000</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2.8969999999999999E-2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>9.3100000000000006E-3</v>
+      </c>
       <c r="E3" s="2"/>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
@@ -5071,11 +5272,17 @@
       <c r="N3" s="3"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>6000</v>
-      </c>
-      <c r="B4" s="2"/>
+        <f t="shared" ref="A4:A16" si="0">A3+1000</f>
+        <v>3000</v>
+      </c>
+      <c r="B4" s="2">
+        <v>6.0650000000000003E-2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.9599999999999999E-2</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
@@ -5084,11 +5291,17 @@
       <c r="N4" s="3"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>8000</v>
-      </c>
-      <c r="B5" s="2"/>
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.11246</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3.3090000000000001E-2</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
@@ -5096,12 +5309,19 @@
       <c r="L5" s="1"/>
       <c r="N5" s="3"/>
       <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S5" s="2"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>10000</v>
-      </c>
-      <c r="B6" s="2"/>
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.16563</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4.7370000000000002E-2</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="H6" s="3"/>
       <c r="I6" s="1"/>
@@ -5109,12 +5329,19 @@
       <c r="L6" s="1"/>
       <c r="N6" s="3"/>
       <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S6" s="2"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>12000</v>
-      </c>
-      <c r="B7" s="2"/>
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.24306</v>
+      </c>
+      <c r="C7" s="2">
+        <v>7.2679999999999995E-2</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="H7" s="3"/>
       <c r="I7" s="1"/>
@@ -5122,12 +5349,19 @@
       <c r="L7" s="1"/>
       <c r="N7" s="3"/>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>14000</v>
-      </c>
-      <c r="B8" s="2"/>
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.32597999999999999</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.10063</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="H8" s="3"/>
       <c r="I8" s="1"/>
@@ -5135,12 +5369,19 @@
       <c r="L8" s="1"/>
       <c r="N8" s="3"/>
       <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S8" s="2"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>16000</v>
-      </c>
-      <c r="B9" s="2"/>
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.42725999999999997</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.13117000000000001</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="H9" s="3"/>
       <c r="I9" s="1"/>
@@ -5148,12 +5389,19 @@
       <c r="L9" s="1"/>
       <c r="N9" s="3"/>
       <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S9" s="2"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>18000</v>
-      </c>
-      <c r="B10" s="2"/>
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.54071000000000002</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.17502000000000001</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="H10" s="3"/>
       <c r="I10" s="1"/>
@@ -5161,12 +5409,19 @@
       <c r="L10" s="1"/>
       <c r="N10" s="3"/>
       <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>20000</v>
-      </c>
-      <c r="B11" s="2"/>
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.67457</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.21023</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="H11" s="3"/>
       <c r="I11" s="1"/>
@@ -5174,12 +5429,19 @@
       <c r="L11" s="1"/>
       <c r="N11" s="3"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S11" s="2"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>22000</v>
-      </c>
-      <c r="B12" s="2"/>
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.81305000000000005</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.27510000000000001</v>
+      </c>
       <c r="E12" s="2"/>
       <c r="H12" s="3"/>
       <c r="I12" s="1"/>
@@ -5187,12 +5449,19 @@
       <c r="L12" s="1"/>
       <c r="N12" s="3"/>
       <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>24000</v>
-      </c>
-      <c r="B13" s="2"/>
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.99312</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.32073000000000002</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="H13" s="3"/>
       <c r="I13" s="1"/>
@@ -5200,12 +5469,19 @@
       <c r="L13" s="1"/>
       <c r="N13" s="3"/>
       <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>26000</v>
-      </c>
-      <c r="B14" s="2"/>
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1.1511499999999999</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.38468999999999998</v>
+      </c>
       <c r="E14" s="2"/>
       <c r="H14" s="3"/>
       <c r="I14" s="1"/>
@@ -5213,12 +5489,19 @@
       <c r="L14" s="1"/>
       <c r="N14" s="3"/>
       <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>28000</v>
-      </c>
-      <c r="B15" s="2"/>
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.36422</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.45236999999999999</v>
+      </c>
       <c r="E15" s="2"/>
       <c r="H15" s="3"/>
       <c r="I15" s="1"/>
@@ -5226,12 +5509,19 @@
       <c r="L15" s="1"/>
       <c r="N15" s="3"/>
       <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>30000</v>
-      </c>
-      <c r="B16" s="2"/>
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.5779000000000001</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.51902999999999999</v>
+      </c>
       <c r="E16" s="2"/>
       <c r="H16" s="3"/>
       <c r="I16" s="1"/>
@@ -5239,8 +5529,9 @@
       <c r="L16" s="1"/>
       <c r="N16" s="3"/>
       <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="S16" s="2"/>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
       <c r="E17" s="2"/>
       <c r="H17" s="3"/>
@@ -5249,10 +5540,18 @@
       <c r="L17" s="1"/>
       <c r="N17" s="3"/>
       <c r="O17" s="1"/>
+      <c r="S17" s="2"/>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="S18" s="2"/>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="S19" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5288,10 +5587,14 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2000</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2"/>
+        <v>1000</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1.098E-2</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1.0499999999999999E-3</v>
+      </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -5304,10 +5607,15 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4000</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
+        <f>A2+1000</f>
+        <v>2000</v>
+      </c>
+      <c r="B3" s="3">
+        <v>4.5809999999999997E-2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.2599999999999999E-3</v>
+      </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -5320,10 +5628,15 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>6000</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2"/>
+        <f t="shared" ref="A4:A16" si="0">A3+1000</f>
+        <v>3000</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.10169</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7.6899999999999998E-3</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -5336,10 +5649,15 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>8000</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.17945</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.332E-2</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -5352,10 +5670,15 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>10000</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="2"/>
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.27944999999999998</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.9290000000000002E-2</v>
+      </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -5368,10 +5691,15 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>12000</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.38246999999999998</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4.2799999999999998E-2</v>
+      </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -5384,10 +5712,15 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>14000</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="2"/>
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.52719000000000005</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4.1180000000000001E-2</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -5400,10 +5733,15 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>16000</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.70315000000000005</v>
+      </c>
+      <c r="C9" s="3">
+        <v>5.4949999999999999E-2</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -5416,10 +5754,15 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>18000</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.88338000000000005</v>
+      </c>
+      <c r="C10" s="3">
+        <v>7.3660000000000003E-2</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -5432,10 +5775,15 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>20000</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1.09884</v>
+      </c>
+      <c r="C11" s="3">
+        <v>9.7879999999999995E-2</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -5448,10 +5796,15 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>22000</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1.36015</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.11326</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -5464,10 +5817,15 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>24000</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1.6630100000000001</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.14346999999999999</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -5480,10 +5838,15 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>26000</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1.97478</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.17679</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -5496,10 +5859,15 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>28000</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2.34335</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.20202000000000001</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -5512,10 +5880,15 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>30000</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2.73854</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.24174999999999999</v>
+      </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -5566,10 +5939,15 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2000</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2"/>
+        <v>1000</v>
+      </c>
+      <c r="B2" s="3">
+        <f>8.31999996080412*10^-4</f>
+        <v>8.3199999608041199E-4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2.6577999997243699E-3</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -5579,10 +5957,15 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4000</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
+        <f>A2+1000</f>
+        <v>2000</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.27400000565103E-3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>8.4587999990617304E-3</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -5592,10 +5975,15 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>6000</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2"/>
+        <f t="shared" ref="A4:A16" si="0">A3+1000</f>
+        <v>3000</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1.8180000006395799E-3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.84257000000798E-2</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -5605,10 +5993,15 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>8000</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2.5159999950119501E-3</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3.13871999987895E-2</v>
+      </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -5618,10 +6011,15 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>10000</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="2"/>
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2.9709999944316202E-3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4.7633199999836499E-2</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -5631,10 +6029,15 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>12000</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="B7" s="3">
+        <v>3.53399999767134E-3</v>
+      </c>
+      <c r="C7" s="2">
+        <v>7.3047699999733595E-2</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -5644,10 +6047,15 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>14000</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="2"/>
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="B8" s="3">
+        <v>4.1819999933068097E-3</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.100573699999586</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -5657,10 +6065,15 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>16000</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="B9" s="3">
+        <v>4.7510000058537099E-3</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.13349120000020701</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -5670,10 +6083,15 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>18000</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
+      <c r="B10" s="3">
+        <v>5.6229999972856604E-3</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.17780250000032499</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -5683,10 +6101,15 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>20000</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="B11" s="3">
+        <v>6.70499999614548E-3</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.227332300000853</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -5696,10 +6119,15 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>22000</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="B12" s="3">
+        <v>7.6390000049286703E-3</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.26611559999946599</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -5709,10 +6137,15 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>24000</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="B13" s="3">
+        <v>8.2920000022568205E-3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.33415179999974498</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -5722,10 +6155,15 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>26000</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
+      <c r="B14" s="3">
+        <v>8.6589999955322093E-3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.38591469999846501</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -5735,10 +6173,15 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>28000</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="B15" s="3">
+        <v>8.9970000044559094E-3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.45124240000040999</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -5748,10 +6191,15 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>30000</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="B16" s="3">
+        <v>9.69400000030873E-3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.54056039999886696</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -5775,6 +6223,7 @@
   <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.85546875" customWidth="1"/>
@@ -5803,10 +6252,14 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2000</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2"/>
+        <v>1000</v>
+      </c>
+      <c r="B2" s="4">
+        <v>50</v>
+      </c>
+      <c r="C2" s="5">
+        <v>12</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -5819,10 +6272,15 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4000</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
+        <f>A2+1000</f>
+        <v>2000</v>
+      </c>
+      <c r="B3" s="4">
+        <v>50</v>
+      </c>
+      <c r="C3" s="5">
+        <v>13</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -5835,10 +6293,15 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>6000</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="2"/>
+        <f t="shared" ref="A4:A16" si="0">A3+1000</f>
+        <v>3000</v>
+      </c>
+      <c r="B4" s="4">
+        <v>64</v>
+      </c>
+      <c r="C4" s="5">
+        <v>13</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -5851,10 +6314,15 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>8000</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="B5" s="4">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5">
+        <v>14</v>
+      </c>
       <c r="D5" s="3"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -5867,10 +6335,15 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>10000</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="2"/>
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="B6" s="4">
+        <v>84</v>
+      </c>
+      <c r="C6" s="5">
+        <v>14</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -5883,10 +6356,15 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>12000</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="B7" s="4">
+        <v>102</v>
+      </c>
+      <c r="C7" s="5">
+        <v>14</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -5899,10 +6377,15 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>14000</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="2"/>
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+      <c r="B8" s="4">
+        <v>113</v>
+      </c>
+      <c r="C8" s="5">
+        <v>14</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -5915,10 +6398,15 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>16000</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="B9" s="4">
+        <v>122</v>
+      </c>
+      <c r="C9" s="5">
+        <v>15</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -5931,10 +6419,15 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>18000</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
+      <c r="B10" s="4">
+        <v>122</v>
+      </c>
+      <c r="C10" s="5">
+        <v>15</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -5947,10 +6440,15 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>20000</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="B11" s="4">
+        <v>143</v>
+      </c>
+      <c r="C11" s="5">
+        <v>15</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -5963,10 +6461,15 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>22000</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="B12" s="4">
+        <v>165</v>
+      </c>
+      <c r="C12" s="5">
+        <v>15</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -5979,10 +6482,15 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>24000</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="B13" s="4">
+        <v>165</v>
+      </c>
+      <c r="C13" s="5">
+        <v>15</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -5995,10 +6503,15 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>26000</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
+      <c r="B14" s="4">
+        <v>173</v>
+      </c>
+      <c r="C14" s="5">
+        <v>15</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -6011,10 +6524,15 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>28000</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
+        <f t="shared" si="0"/>
+        <v>14000</v>
+      </c>
+      <c r="B15" s="4">
+        <v>185</v>
+      </c>
+      <c r="C15" s="5">
+        <v>15</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -6027,10 +6545,15 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>30000</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="B16" s="4">
+        <v>204</v>
+      </c>
+      <c r="C16" s="5">
+        <v>16</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
